--- a/assets/templates/master_db_template.xlsx
+++ b/assets/templates/master_db_template.xlsx
@@ -18,18 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -43,17 +38,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -97,21 +87,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -482,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -507,365 +494,263 @@
     <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>내부 고유키 (자동생성)</t>
+          <t>상품ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>13자리 ISBN</t>
+          <t>ISBN</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>원제목</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>권수 포함 조합명 (자동생성)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>저자명</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>출판사명</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>정가 (숫자)</t>
+          <t>도서명</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>도서명_조합</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>저자</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>출판사</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>정가</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>희망 판매가 (숫자)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>가격조정 최저 허용가</t>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>최저허용가</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>최상/상/중/하</t>
+          <t>상태등급</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>재고 수량</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>스마트스토어 등록 Y/N</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>알라딘 등록 Y/N</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>예스24 등록 Y/N</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>알라딘 등록 후 코드</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>개똥이네 등록 후 코드</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>북코아 등록 후 코드</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>판매 완료 Y/N</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>판매된 채널명</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>미처리/처리중/완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>상품ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ISBN</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>도서명</t>
+          <t>재고수량</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>등록대상_스마트</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>등록대상_알라딘</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>등록대상_예스24</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>알라딘_상품코드</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>개똥이네_상품코드</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>북코아_상품코드</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>판매완료여부</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>판매채널</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>처리상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>9788936434267</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>채식주의자</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>도서명_조합</t>
+          <t>채식주의자</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>저자</t>
+          <t>한강</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>출판사</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>정가</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>최저허용가</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>상태등급</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>재고수량</t>
-        </is>
+          <t>창비</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>등록대상_스마트</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>등록대상_알라딘</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>등록대상_예스24</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>알라딘_상품코드</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>개똥이네_상품코드</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>북코아_상품코드</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>판매완료여부</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>판매채널</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>처리상태</t>
+          <t>미처리</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>9788936434267</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>채식주의자</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>채식주의자</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>한강</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>창비</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="n">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>9788954651135</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>82년생 김지영</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>82년생 김지영</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>조남주</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>민음사</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>최상</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>ALI-12345</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>미처리</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>9788954651135</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>82년생 김지영</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>82년생 김지영</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>조남주</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>민음사</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>최상</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>ALI-12345</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>미처리</t>
         </is>
@@ -890,96 +775,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>상품ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>비워두세요. 시스템이 자동 생성합니다.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>상태등급</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>최상 / 상 / 중 / 하 중 하나 입력</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>등록대상_*</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>등록할 플랫폼은 Y, 아니면 N 입력</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>판매완료여부</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>판매 완료 시 Y로 변경 → 모듈2가 자동 처리</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>처리상태</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>미처리 / 처리중 / 완료 (시스템이 자동 변경)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>빨간 헤더</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>필수 입력 항목</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>파란 헤더</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>선택 입력 항목</t>
         </is>
